--- a/public/downloads/TangNitrate2024.xlsx
+++ b/public/downloads/TangNitrate2024.xlsx
@@ -1575,16 +1575,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2426186623911062</v>
+        <v>-0.2588821573920441</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1011562068954486</v>
+        <v>0.09883285046674319</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1011562068954486</v>
+        <v>0.09883285046674319</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -1634,16 +1634,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3973388828618449</v>
+        <v>-0.389594879218361</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.0712718778970839</v>
+        <v>0.07016559166230049</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.0712718778970839</v>
+        <v>0.07016559166230049</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -1693,16 +1693,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.439263532796002</v>
+        <v>-0.4348137569362009</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1067898355324698</v>
+        <v>0.106154153266784</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1067898355324698</v>
+        <v>0.106154153266784</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -1752,16 +1752,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.3344184341682013</v>
+        <v>-0.2706589355562912</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1147763793252954</v>
+        <v>0.1062548690583119</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1329423752763645</v>
+        <v>0.1143008314025256</v>
       </c>
       <c r="R6" s="5">
         <v>6</v>
@@ -1811,13 +1811,13 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.1688056452009115</v>
+        <v>-0.184219444055211</v>
       </c>
       <c r="O7" s="5">
         <v>6</v>
       </c>
       <c r="P7" s="4">
-        <v>0.4019512270908138</v>
+        <v>0.4041531983557137</v>
       </c>
       <c r="Q7" s="4">
         <v>0.1305452156942817</v>
@@ -1927,16 +1927,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.1230416813690223</v>
+        <v>0.1099925283055168</v>
       </c>
       <c r="O9" s="5">
         <v>6</v>
       </c>
       <c r="P9" s="4">
-        <v>0.4345909243590825</v>
+        <v>0.4363934004658235</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1125699970275302</v>
+        <v>0.1124980269748104</v>
       </c>
       <c r="R9" s="5">
         <v>6</v>
@@ -1986,13 +1986,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.05131701684894807</v>
+        <v>0.04108780376397192</v>
       </c>
       <c r="O10" s="5">
         <v>6</v>
       </c>
       <c r="P10" s="4">
-        <v>1.369073728186922</v>
+        <v>1.367612412031926</v>
       </c>
       <c r="Q10" s="4">
         <v>0.07445109762573783</v>
@@ -2045,16 +2045,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.0829135030445137</v>
+        <v>-0.03381162723076869</v>
       </c>
       <c r="O11" s="5">
         <v>5</v>
       </c>
       <c r="P11" s="4">
-        <v>0.3413319048368479</v>
+        <v>0.324964612898933</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1240288501106096</v>
+        <v>0.1142084749478606</v>
       </c>
       <c r="R11" s="5">
         <v>5</v>
@@ -2227,16 +2227,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3556742156496122</v>
+        <v>-0.2149122476512275</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3447958725556251</v>
+        <v>0.3214887566329188</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3447958725556251</v>
+        <v>0.3214887566329188</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -2286,16 +2286,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.7397204525072344</v>
+        <v>-0.7903908219232108</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2146779162457631</v>
+        <v>0.2074392920434807</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2146779162457631</v>
+        <v>0.2074392920434807</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -2345,16 +2345,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.008884823257436</v>
+        <v>-0.9925706562789856</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1132398565358907</v>
+        <v>0.110909261253255</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1132398565358907</v>
+        <v>0.110909261253255</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -2404,16 +2404,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.121284035537731</v>
+        <v>-1.05966905373316</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1514434491776531</v>
+        <v>0.1599943734797437</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1639839383779973</v>
+        <v>0.163690853096341</v>
       </c>
       <c r="R6" s="5">
         <v>6</v>
@@ -2463,16 +2463,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.07112640952473157</v>
+        <v>-0.142679831944406</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>0.647875822197862</v>
+        <v>0.6173320734165567</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.7657130998905631</v>
+        <v>0.7229518515967357</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -2579,16 +2579,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.4742716526852746</v>
+        <v>0.2398990474393941</v>
       </c>
       <c r="O9" s="5">
         <v>7</v>
       </c>
       <c r="P9" s="4">
-        <v>0.5150695115943174</v>
+        <v>0.4669783752350278</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5150695115943174</v>
+        <v>0.4669783752350278</v>
       </c>
       <c r="R9" s="5">
         <v>7</v>
@@ -2638,16 +2638,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.3635568374957074</v>
+        <v>-0.2053941234116792</v>
       </c>
       <c r="O10" s="5">
         <v>5</v>
       </c>
       <c r="P10" s="4">
-        <v>0.7535827720156314</v>
+        <v>0.7761774454562068</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.3100283256528201</v>
+        <v>0.2783957828360144</v>
       </c>
       <c r="R10" s="5">
         <v>5</v>
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.1935135835368177</v>
+        <v>-0.2889021337286977</v>
       </c>
       <c r="O11" s="5">
         <v>6</v>
@@ -2879,16 +2879,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1410870591449718</v>
+        <v>-0.2894360280831059</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2925289560596211</v>
+        <v>0.269887352519913</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2925289560596211</v>
+        <v>0.269887352519913</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -2938,16 +2938,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2753752217077298</v>
+        <v>-0.4058320674288796</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1780279645867315</v>
+        <v>0.159391272340853</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1780279645867315</v>
+        <v>0.159391272340853</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -2997,16 +2997,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.290591458530535</v>
+        <v>-0.3372655722969178</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1007293605602837</v>
+        <v>0.094061630022229</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1007293605602837</v>
+        <v>0.094061630022229</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -3056,16 +3056,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.3016318435941363</v>
+        <v>-0.2964899299148449</v>
       </c>
       <c r="O6" s="5">
         <v>5</v>
       </c>
       <c r="P6" s="4">
-        <v>0.0707574409187423</v>
+        <v>0.07002288182170067</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.06429779790575693</v>
+        <v>0.06326941516989866</v>
       </c>
       <c r="R6" s="5">
         <v>5</v>
@@ -3115,16 +3115,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.07651242889509417</v>
+        <v>-0.1038113873473243</v>
       </c>
       <c r="O7" s="5">
         <v>7</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1053413366139875</v>
+        <v>0.1002394051790757</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1053413366139875</v>
+        <v>0.1002394051790757</v>
       </c>
       <c r="R7" s="5">
         <v>7</v>
@@ -3231,16 +3231,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.1747934375057157</v>
+        <v>0.0162051946184798</v>
       </c>
       <c r="O9" s="5">
         <v>7</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2647151005466552</v>
+        <v>0.2297773410206407</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2647151005466552</v>
+        <v>0.2297773410206407</v>
       </c>
       <c r="R9" s="5">
         <v>7</v>
@@ -3290,16 +3290,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.02105426796903081</v>
+        <v>0.01966169883624502</v>
       </c>
       <c r="O10" s="5">
         <v>7</v>
       </c>
       <c r="P10" s="4">
-        <v>0.09534316234360363</v>
+        <v>0.09514422389606279</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.09534316234360363</v>
+        <v>0.09514422389606279</v>
       </c>
       <c r="R10" s="5">
         <v>7</v>
@@ -3349,16 +3349,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.01205346129432498</v>
+        <v>-0.1260993045167464</v>
       </c>
       <c r="O11" s="5">
         <v>6</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2430568741038186</v>
+        <v>0.2114801852169155</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.2430568741038186</v>
+        <v>0.2114801852169155</v>
       </c>
       <c r="R11" s="5">
         <v>6</v>
@@ -3531,16 +3531,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3635340587674624</v>
+        <v>-0.3947294890422199</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.0980156578719901</v>
+        <v>0.09355916783273902</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.0980156578719901</v>
+        <v>0.09355916783273902</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -3590,16 +3590,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5186572132734</v>
+        <v>-0.5354824986352469</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.0940168807885909</v>
+        <v>0.09161326859404133</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.0940168807885909</v>
+        <v>0.09161326859404133</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -3649,16 +3649,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5748166884046181</v>
+        <v>-0.5703170176057029</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.05823060499571919</v>
+        <v>0.05758779488158845</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.05823060499571919</v>
+        <v>0.05758779488158845</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -3708,16 +3708,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.5105244748358798</v>
+        <v>-0.5231244699753006</v>
       </c>
       <c r="O6" s="5">
         <v>7</v>
       </c>
       <c r="P6" s="4">
-        <v>0.047397464885001</v>
+        <v>0.04447093587909227</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.047397464885001</v>
+        <v>0.04447093587909227</v>
       </c>
       <c r="R6" s="5">
         <v>7</v>
@@ -3767,16 +3767,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.1637724230567983</v>
+        <v>-0.07466894856770523</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>1.399392746533392</v>
+        <v>1.386663678749236</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1611460093481583</v>
+        <v>0.1433253144503396</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -3883,16 +3883,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.05329026270374015</v>
+        <v>0.08369119521375978</v>
       </c>
       <c r="O9" s="5">
         <v>6</v>
       </c>
       <c r="P9" s="4">
-        <v>0.9262375948650775</v>
+        <v>0.9148308425839267</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.09302754593591089</v>
+        <v>0.08478649035957157</v>
       </c>
       <c r="R9" s="5">
         <v>6</v>
@@ -3942,16 +3942,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.02382944292488294</v>
+        <v>-0.08648983724924619</v>
       </c>
       <c r="O10" s="5">
         <v>6</v>
       </c>
       <c r="P10" s="4">
-        <v>2.526355276975924</v>
+        <v>2.515129618098269</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.127049450191003</v>
+        <v>0.1243962472211327</v>
       </c>
       <c r="R10" s="5">
         <v>6</v>
@@ -4001,16 +4001,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.2595328615811013</v>
+        <v>-0.2989786102662038</v>
       </c>
       <c r="O11" s="5">
         <v>5</v>
       </c>
       <c r="P11" s="4">
-        <v>0.6378391598590193</v>
+        <v>0.6251723579110452</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.07181627776386448</v>
+        <v>0.04872696568927495</v>
       </c>
       <c r="R11" s="5">
         <v>5</v>
@@ -4183,16 +4183,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3802914107790067</v>
+        <v>-0.2338435827987269</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3200933406601971</v>
+        <v>0.2991722223773</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3200933406601971</v>
+        <v>0.2991722223773</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -4242,16 +4242,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3737178928453692</v>
+        <v>-0.3175501310761319</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3372334875139688</v>
+        <v>0.3292095215469349</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3372334875139688</v>
+        <v>0.3292095215469349</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -4301,16 +4301,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3232017090693781</v>
+        <v>-0.328795131194056</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2057889082499635</v>
+        <v>0.2049898479464381</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2057889082499635</v>
+        <v>0.2049898479464381</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -4360,16 +4360,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.3420902295900825</v>
+        <v>-0.3055143950186903</v>
       </c>
       <c r="O6" s="5">
         <v>7</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1076600113858371</v>
+        <v>0.09621606515637333</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1076600113858371</v>
+        <v>0.09621606515637333</v>
       </c>
       <c r="R6" s="5">
         <v>7</v>
@@ -4419,13 +4419,13 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.1935797164193597</v>
+        <v>-0.1704125228570774</v>
       </c>
       <c r="O7" s="5">
         <v>6</v>
       </c>
       <c r="P7" s="4">
-        <v>1.05692435449765</v>
+        <v>1.053614755417324</v>
       </c>
       <c r="Q7" s="4">
         <v>0.3639347625072939</v>
@@ -4535,16 +4535,16 @@
         <v>1</v>
       </c>
       <c r="N9" s="4">
-        <v>1.086375659861265</v>
+        <v>0.05289187206653878</v>
       </c>
       <c r="O9" s="5">
         <v>7</v>
       </c>
       <c r="P9" s="4">
-        <v>1.993807471264183</v>
+        <v>1.361049923848831</v>
       </c>
       <c r="Q9" s="4">
-        <v>1.16305435823744</v>
+        <v>0.2525899216204077</v>
       </c>
       <c r="R9" s="5">
         <v>6</v>
@@ -4594,13 +4594,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.1685660057598094</v>
+        <v>0.1529617686501297</v>
       </c>
       <c r="O10" s="5">
         <v>6</v>
       </c>
       <c r="P10" s="4">
-        <v>1.025483620106787</v>
+        <v>1.023254443376832</v>
       </c>
       <c r="Q10" s="4">
         <v>0.2413012244523998</v>
@@ -4653,7 +4653,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.3361183928158425</v>
+        <v>-0.5127336245641345</v>
       </c>
       <c r="O11" s="5">
         <v>5</v>
@@ -4662,7 +4662,7 @@
         <v>1.426912025979618</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.3510874451359268</v>
+        <v>0.3157643987862684</v>
       </c>
       <c r="R11" s="5">
         <v>5</v>
@@ -4835,16 +4835,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5572163887627539</v>
+        <v>-0.6070879220897041</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.113072657234235</v>
+        <v>0.1059481524732421</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.113072657234235</v>
+        <v>0.1059481524732421</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -4894,16 +4894,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.7503383217481314</v>
+        <v>-0.7039769616021658</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1677561395668558</v>
+        <v>0.1503051108094431</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1677561395668558</v>
+        <v>0.1503051108094431</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -4953,16 +4953,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.8926500438995261</v>
+        <v>-0.9162537928132224</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.0913136007914044</v>
+        <v>0.08794163666087636</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.0913136007914044</v>
+        <v>0.08794163666087636</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -5012,16 +5012,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.124883997136446</v>
+        <v>-1.178506561294853</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1152391302261787</v>
+        <v>0.1187191421218553</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1175848007713082</v>
+        <v>0.1127077206231964</v>
       </c>
       <c r="R6" s="5">
         <v>6</v>
@@ -5071,16 +5071,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.5951082384352049</v>
+        <v>-0.6162177538499236</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>3.087110394571002</v>
+        <v>3.090126039630247</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.09382130523066734</v>
+        <v>0.08959940214772359</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -5187,13 +5187,13 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.2205719402584994</v>
+        <v>-0.2092659583540808</v>
       </c>
       <c r="O9" s="5">
         <v>6</v>
       </c>
       <c r="P9" s="4">
-        <v>1.235872361413948</v>
+        <v>1.234257221141888</v>
       </c>
       <c r="Q9" s="4">
         <v>0.1480150975373059</v>
@@ -5246,13 +5246,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.2480162951681753</v>
+        <v>0.2192477425851393</v>
       </c>
       <c r="O10" s="5">
         <v>6</v>
       </c>
       <c r="P10" s="4">
-        <v>0.5736812500674119</v>
+        <v>0.5695714568412639</v>
       </c>
       <c r="Q10" s="4">
         <v>0.09783832485785145</v>
@@ -5305,7 +5305,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.6543434904720925</v>
+        <v>-0.658775494681322</v>
       </c>
       <c r="O11" s="5">
         <v>5</v>
@@ -5314,7 +5314,7 @@
         <v>0.435120467914506</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1179239646179485</v>
+        <v>0.1170375637761026</v>
       </c>
       <c r="R11" s="5">
         <v>5</v>
@@ -5487,16 +5487,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2671691284953623</v>
+        <v>-0.2823554217357103</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1043865784601204</v>
+        <v>0.1022171079972135</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1043865784601204</v>
+        <v>0.1022171079972135</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -5546,16 +5546,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1691012780949135</v>
+        <v>-0.1517835777049275</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.08234141853623478</v>
+        <v>0.07986746133766534</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08234141853623478</v>
+        <v>0.07986746133766534</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -5605,16 +5605,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.03809935018318659</v>
+        <v>0.002627519243104004</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.06482202801494075</v>
+        <v>0.05900390381118496</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06482202801494075</v>
+        <v>0.05900390381118496</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -5664,13 +5664,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.01537760948729024</v>
+        <v>0.01687445753124983</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
       </c>
       <c r="P6" s="4">
-        <v>0.06984072832276493</v>
+        <v>0.0700545637576163</v>
       </c>
       <c r="Q6" s="4">
         <v>0.06514053019780726</v>
@@ -5723,16 +5723,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.003399794488351609</v>
+        <v>0.0725043743913627</v>
       </c>
       <c r="O7" s="5">
         <v>7</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1066716762631603</v>
+        <v>0.09679959341987297</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1066716762631603</v>
+        <v>0.09679959341987297</v>
       </c>
       <c r="R7" s="5">
         <v>7</v>
@@ -5839,16 +5839,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.01552373782604935</v>
+        <v>0.04347474981476829</v>
       </c>
       <c r="O9" s="5">
         <v>7</v>
       </c>
       <c r="P9" s="4">
-        <v>0.1291759430284669</v>
+        <v>0.1206032054973724</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1291759430284669</v>
+        <v>0.1206032054973724</v>
       </c>
       <c r="R9" s="5">
         <v>7</v>
@@ -5898,16 +5898,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.1419937848066886</v>
+        <v>-0.1572908604867109</v>
       </c>
       <c r="O10" s="5">
         <v>7</v>
       </c>
       <c r="P10" s="4">
-        <v>0.03319566555535983</v>
+        <v>0.03101036902964235</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.03319566555535983</v>
+        <v>0.03101036902964235</v>
       </c>
       <c r="R10" s="5">
         <v>7</v>
@@ -5957,16 +5957,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.1179296090164398</v>
+        <v>-0.09647712114019136</v>
       </c>
       <c r="O11" s="5">
         <v>6</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1138098731361323</v>
+        <v>0.1123162326069552</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1138098731361323</v>
+        <v>0.1123162326069552</v>
       </c>
       <c r="R11" s="5">
         <v>6</v>
@@ -6139,16 +6139,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.739750206394619</v>
+        <v>-0.7375217801891427</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06252597725540041</v>
+        <v>0.06220763065461808</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06252597725540041</v>
+        <v>0.06220763065461808</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -6198,16 +6198,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.8171259392953046</v>
+        <v>-0.8223395865207284</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06907315255941056</v>
+        <v>0.06832834581292145</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06907315255941056</v>
+        <v>0.06832834581292145</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -6257,16 +6257,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.8303634711025596</v>
+        <v>-0.8229925509003806</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.0496103013571609</v>
+        <v>0.04855731275684962</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.0496103013571609</v>
+        <v>0.04855731275684962</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -6316,16 +6316,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.843788373166413</v>
+        <v>-0.8239618386578673</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
       </c>
       <c r="P6" s="4">
-        <v>0.04508166163871579</v>
+        <v>0.0437297688144402</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.04210923389311005</v>
+        <v>0.03722760318003093</v>
       </c>
       <c r="R6" s="5">
         <v>6</v>
@@ -6375,13 +6375,13 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.8969166715851381</v>
+        <v>-0.905335666851899</v>
       </c>
       <c r="O7" s="5">
         <v>6</v>
       </c>
       <c r="P7" s="4">
-        <v>0.09953817601776413</v>
+        <v>0.1007408896273014</v>
       </c>
       <c r="Q7" s="4">
         <v>0.0778908790883482</v>
@@ -6491,16 +6491,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.6684528017176606</v>
+        <v>-0.6692165572531099</v>
       </c>
       <c r="O9" s="5">
         <v>7</v>
       </c>
       <c r="P9" s="4">
-        <v>0.1294278165358833</v>
+        <v>0.1293187086022477</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1294278165358833</v>
+        <v>0.1293187086022477</v>
       </c>
       <c r="R9" s="5">
         <v>7</v>
@@ -6550,16 +6550,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.4655289838270257</v>
+        <v>0.4773375448785373</v>
       </c>
       <c r="O10" s="5">
         <v>7</v>
       </c>
       <c r="P10" s="4">
-        <v>0.05683617914414824</v>
+        <v>0.05514924185107516</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.05683617914414824</v>
+        <v>0.05514924185107516</v>
       </c>
       <c r="R10" s="5">
         <v>7</v>
@@ -6609,16 +6609,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.9714247002163384</v>
+        <v>-0.9630777538077542</v>
       </c>
       <c r="O11" s="5">
         <v>6</v>
       </c>
       <c r="P11" s="4">
-        <v>0.09327909584883465</v>
+        <v>0.09268080649114552</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.09327909584883465</v>
+        <v>0.09268080649114552</v>
       </c>
       <c r="R11" s="5">
         <v>6</v>
@@ -6791,16 +6791,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2140030668555765</v>
+        <v>-0.2396654426593248</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1219340496428073</v>
+        <v>0.1182679959565576</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1219340496428073</v>
+        <v>0.1182679959565576</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -6850,16 +6850,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1064075417120142</v>
+        <v>-0.08974445127388186</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.08844406386552087</v>
+        <v>0.08606362237435913</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08844406386552087</v>
+        <v>0.08606362237435913</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -6909,16 +6909,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.02472263410789008</v>
+        <v>0.05604875751673966</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.06366598050374997</v>
+        <v>0.0575661575801037</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06366598050374997</v>
+        <v>0.0575661575801037</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -6968,16 +6968,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.09454576155137288</v>
+        <v>0.1029261339536003</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
       </c>
       <c r="P6" s="4">
-        <v>0.05721974520166236</v>
+        <v>0.05710009824489885</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.05614212220622308</v>
+        <v>0.05460580535629441</v>
       </c>
       <c r="R6" s="5">
         <v>6</v>
@@ -7027,16 +7027,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.09210970661816045</v>
+        <v>0.08711382278123914</v>
       </c>
       <c r="O7" s="5">
         <v>7</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1029404078734151</v>
+        <v>0.1022267101824263</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1029404078734151</v>
+        <v>0.1022267101824263</v>
       </c>
       <c r="R7" s="5">
         <v>7</v>
@@ -7086,16 +7086,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.09449262620111192</v>
+        <v>0.1062249419155901</v>
       </c>
       <c r="O8" s="5">
         <v>5</v>
       </c>
       <c r="P8" s="4">
-        <v>0.07897455199760088</v>
+        <v>0.07668137431079559</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.05100556216173289</v>
+        <v>0.04779511340020548</v>
       </c>
       <c r="R8" s="5">
         <v>5</v>
@@ -7145,16 +7145,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.1033009777617941</v>
+        <v>0.1397087137811379</v>
       </c>
       <c r="O9" s="5">
         <v>7</v>
       </c>
       <c r="P9" s="4">
-        <v>0.1261993113968179</v>
+        <v>0.1115653226552339</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1261993113968179</v>
+        <v>0.1115653226552339</v>
       </c>
       <c r="R9" s="5">
         <v>7</v>
@@ -7204,16 +7204,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.1854713413418563</v>
+        <v>-0.1914373780018934</v>
       </c>
       <c r="O10" s="5">
         <v>7</v>
       </c>
       <c r="P10" s="4">
-        <v>0.02411196148275093</v>
+        <v>0.02325967053131706</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.02411196148275093</v>
+        <v>0.02325967053131706</v>
       </c>
       <c r="R10" s="5">
         <v>7</v>
@@ -7263,16 +7263,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.03215485949902034</v>
+        <v>0.0121026379547029</v>
       </c>
       <c r="O11" s="5">
         <v>6</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1006489291511375</v>
+        <v>0.08877531854825331</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1006489291511375</v>
+        <v>0.08877531854825331</v>
       </c>
       <c r="R11" s="5">
         <v>6</v>
@@ -7445,16 +7445,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4738930718480666</v>
+        <v>-0.3927499214405703</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1370496928746239</v>
+        <v>0.1254578142449816</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1370496928746239</v>
+        <v>0.1254578142449816</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -7504,16 +7504,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2751627622274118</v>
+        <v>-0.2570729601066137</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1425069206348602</v>
+        <v>0.1399226631890319</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1425069206348602</v>
+        <v>0.1399226631890319</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -7563,16 +7563,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.05670683036856009</v>
+        <v>-0.08574356461027044</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.06708923596246584</v>
+        <v>0.06294113107079292</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06708923596246584</v>
+        <v>0.06294113107079292</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -7622,13 +7622,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.06286791196060044</v>
+        <v>0.07052943975760506</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
       </c>
       <c r="P6" s="4">
-        <v>0.09640863356703659</v>
+        <v>0.09750313753803727</v>
       </c>
       <c r="Q6" s="4">
         <v>0.0617870669072221</v>
@@ -7681,16 +7681,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.214854070535397</v>
+        <v>-0.2393781783957838</v>
       </c>
       <c r="O7" s="5">
         <v>6</v>
       </c>
       <c r="P7" s="4">
-        <v>0.161680528825197</v>
+        <v>0.1577241540962758</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1615665678186247</v>
+        <v>0.1610381486116144</v>
       </c>
       <c r="R7" s="5">
         <v>6</v>
@@ -7797,16 +7797,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.4022394102092776</v>
+        <v>-0.4000469364473265</v>
       </c>
       <c r="O9" s="5">
         <v>7</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2085610720635115</v>
+        <v>0.2082478615260899</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2085610720635115</v>
+        <v>0.2082478615260899</v>
       </c>
       <c r="R9" s="5">
         <v>7</v>
@@ -7856,13 +7856,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.151453045341737</v>
+        <v>0.1374908889883955</v>
       </c>
       <c r="O10" s="5">
         <v>6</v>
       </c>
       <c r="P10" s="4">
-        <v>0.395603602497857</v>
+        <v>0.3936090087330939</v>
       </c>
       <c r="Q10" s="4">
         <v>0.1108555262186736</v>
@@ -7915,7 +7915,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.4368511849600877</v>
+        <v>-0.4299653356847575</v>
       </c>
       <c r="O11" s="5">
         <v>6</v>
@@ -8061,13 +8061,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.5021121403088075</v>
+        <v>0.4964220401875977</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1333257620271874</v>
+        <v>0.128206227184819</v>
       </c>
       <c r="J3" s="4">
-        <v>3.158767620092581</v>
+        <v>3.152383087150948</v>
       </c>
       <c r="K3" s="4">
         <v>84.05310511301255</v>
@@ -8111,13 +8111,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.2285106803203371</v>
+        <v>0.2222201029323016</v>
       </c>
       <c r="I4" s="4">
-        <v>0.177934366919138</v>
+        <v>0.1679922854966448</v>
       </c>
       <c r="J4" s="4">
-        <v>0.1844513452344511</v>
+        <v>0.1848390421859397</v>
       </c>
       <c r="K4" s="4">
         <v>76.98650427913157</v>
@@ -8143,13 +8143,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>79.03225806451613</v>
+        <v>88.70967741935483</v>
       </c>
       <c r="C5" s="3">
         <v>9.67741935483871</v>
       </c>
       <c r="D5" s="3">
-        <v>11.29032258064516</v>
+        <v>1.612903225806452</v>
       </c>
       <c r="E5" s="3">
         <v>0</v>
@@ -8158,16 +8158,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="3">
-        <v>11.29032258064516</v>
+        <v>1.612903225806452</v>
       </c>
       <c r="H5" s="4">
-        <v>0.6471189328284752</v>
+        <v>0.4498755126415422</v>
       </c>
       <c r="I5" s="4">
-        <v>0.1330383896023885</v>
+        <v>0.1292736278353418</v>
       </c>
       <c r="J5" s="4">
-        <v>0.8686848288067398</v>
+        <v>0.6739739760569724</v>
       </c>
       <c r="K5" s="4">
         <v>82.32170287469873</v>
@@ -8211,13 +8211,13 @@
         <v>1.612903225806452</v>
       </c>
       <c r="H6" s="4">
-        <v>0.3440992695448745</v>
+        <v>0.3163914777531083</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2846230212819794</v>
+        <v>0.2467771681592487</v>
       </c>
       <c r="J6" s="4">
-        <v>0.4108353993107133</v>
+        <v>0.3847800860008471</v>
       </c>
       <c r="K6" s="4">
         <v>83.40410357691505</v>
@@ -8261,13 +8261,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.3118367914245619</v>
+        <v>0.3068922393440516</v>
       </c>
       <c r="I7" s="4">
-        <v>0.1055280714833755</v>
+        <v>0.09926092421073918</v>
       </c>
       <c r="J7" s="4">
-        <v>0.8944347911374463</v>
+        <v>0.8923696605778816</v>
       </c>
       <c r="K7" s="4">
         <v>84.36251920122869</v>
@@ -8311,13 +8311,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.3909445826960586</v>
+        <v>0.3882266846398638</v>
       </c>
       <c r="I8" s="4">
-        <v>0.109151460985663</v>
+        <v>0.1055695697804305</v>
       </c>
       <c r="J8" s="4">
-        <v>1.026233245196231</v>
+        <v>1.024200231057198</v>
       </c>
       <c r="K8" s="4">
         <v>80.10697827518129</v>
@@ -8361,13 +8361,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.4436074052882636</v>
+        <v>0.4345338672295721</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3754556761432552</v>
+        <v>0.3580390137430421</v>
       </c>
       <c r="J9" s="4">
-        <v>0.4622586615327479</v>
+        <v>0.457127391619202</v>
       </c>
       <c r="K9" s="4">
         <v>82.20704410796615</v>
@@ -8411,13 +8411,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.2033898124381089</v>
+        <v>0.1902947376457625</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1689553771494546</v>
+        <v>0.1547116115858499</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1706227296455981</v>
+        <v>0.1573186381701313</v>
       </c>
       <c r="K10" s="4">
         <v>81.1641430765861</v>
@@ -8461,13 +8461,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.7302120503765043</v>
+        <v>0.7238162882189969</v>
       </c>
       <c r="I11" s="4">
-        <v>0.09807441587908457</v>
+        <v>0.09147976827108113</v>
       </c>
       <c r="J11" s="4">
-        <v>2.926004085504862</v>
+        <v>2.924277034085295</v>
       </c>
       <c r="K11" s="4">
         <v>77.20759271450541</v>
@@ -8511,13 +8511,13 @@
         <v>1.612903225806452</v>
       </c>
       <c r="H12" s="4">
-        <v>0.9222493634235781</v>
+        <v>0.8455333811968059</v>
       </c>
       <c r="I12" s="4">
-        <v>0.3684168185732887</v>
+        <v>0.2565730735368561</v>
       </c>
       <c r="J12" s="4">
-        <v>1.132089347339155</v>
+        <v>1.053390352333032</v>
       </c>
       <c r="K12" s="4">
         <v>76.49001536098321</v>
@@ -8561,13 +8561,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.787130966510932</v>
+        <v>0.7840626210376168</v>
       </c>
       <c r="I13" s="4">
-        <v>0.154101448892281</v>
+        <v>0.1492853626604511</v>
       </c>
       <c r="J13" s="4">
-        <v>1.992373389093984</v>
+        <v>1.996467397169586</v>
       </c>
       <c r="K13" s="4">
         <v>81.54158437568546</v>
@@ -8611,13 +8611,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.08790639869961861</v>
+        <v>0.08427564585303114</v>
       </c>
       <c r="I14" s="4">
-        <v>0.08584400582433714</v>
+        <v>0.0819370485048133</v>
       </c>
       <c r="J14" s="4">
-        <v>0.08227416463372758</v>
+        <v>0.07837548781360811</v>
       </c>
       <c r="K14" s="4">
         <v>91.96291419793791</v>
@@ -8661,13 +8661,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.2030960497454586</v>
+        <v>0.2025796094088563</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1249086714729579</v>
+        <v>0.1238325137828749</v>
       </c>
       <c r="J15" s="4">
-        <v>0.1975374916177068</v>
+        <v>0.1964194275689414</v>
       </c>
       <c r="K15" s="4">
         <v>78.59995611147744</v>
@@ -8711,13 +8711,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.08465038836543715</v>
+        <v>0.08002852538934459</v>
       </c>
       <c r="I16" s="4">
-        <v>0.08282787359844514</v>
+        <v>0.07782896043031012</v>
       </c>
       <c r="J16" s="4">
-        <v>0.07998163740851087</v>
+        <v>0.07544302280673744</v>
       </c>
       <c r="K16" s="4">
         <v>92.14669738863324</v>
@@ -8761,13 +8761,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.2519025847650713</v>
+        <v>0.2492500458587691</v>
       </c>
       <c r="I17" s="4">
-        <v>0.1557475148946258</v>
+        <v>0.1532728357136255</v>
       </c>
       <c r="J17" s="4">
-        <v>0.505463072791143</v>
+        <v>0.5045313240387849</v>
       </c>
       <c r="K17" s="4">
         <v>79.13649330700038</v>
@@ -9738,13 +9738,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="5">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C5" s="5">
         <v>6</v>
       </c>
       <c r="D5" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E5" s="5">
         <v>0</v>
@@ -9753,7 +9753,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
@@ -10464,16 +10464,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3308705771913602</v>
+        <v>-0.3003223100895411</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2014540758722507</v>
+        <v>0.197090037714848</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2014540758722507</v>
+        <v>0.197090037714848</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -10523,16 +10523,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4305821204127694</v>
+        <v>-0.5091706435923697</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1466028938382954</v>
+        <v>0.1353759619554954</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1466028938382954</v>
+        <v>0.1353759619554954</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -10582,16 +10582,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4930136390446153</v>
+        <v>-0.4515648807355319</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1198925493255065</v>
+        <v>0.1139712981384946</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1198925493255065</v>
+        <v>0.1139712981384946</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -10641,16 +10641,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.427356350118013</v>
+        <v>-0.3805788390691305</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1069342880913436</v>
+        <v>0.1036391676594316</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.0997817356870251</v>
+        <v>0.08814117667498067</v>
       </c>
       <c r="R6" s="5">
         <v>6</v>
@@ -10700,16 +10700,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.2160294482461419</v>
+        <v>-0.1639922496615327</v>
       </c>
       <c r="O7" s="5">
         <v>6</v>
       </c>
       <c r="P7" s="4">
-        <v>0.3805686920872436</v>
+        <v>0.3669188424553015</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1480330371398142</v>
+        <v>0.1407810789999834</v>
       </c>
       <c r="R7" s="5">
         <v>6</v>
@@ -10759,13 +10759,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.2930638270057291</v>
+        <v>-0.278844270746049</v>
       </c>
       <c r="O8" s="5">
         <v>6</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2882981870988303</v>
+        <v>0.286266821918876</v>
       </c>
       <c r="Q8" s="4">
         <v>0.142032143551963</v>
@@ -10818,16 +10818,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.06511296320422844</v>
+        <v>0.08663956596501521</v>
       </c>
       <c r="O9" s="5">
         <v>6</v>
       </c>
       <c r="P9" s="4">
-        <v>1.474609033085861</v>
+        <v>1.471449761228411</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1242330259434918</v>
+        <v>0.1241349759032649</v>
       </c>
       <c r="R9" s="5">
         <v>6</v>
@@ -10877,13 +10877,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.1733245677417775</v>
+        <v>-0.17624597809845</v>
       </c>
       <c r="O10" s="5">
         <v>6</v>
       </c>
       <c r="P10" s="4">
-        <v>1.105583862488943</v>
+        <v>1.105166518152276</v>
       </c>
       <c r="Q10" s="4">
         <v>0.08242517768242881</v>
@@ -10936,16 +10936,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.1621722506191872</v>
+        <v>-0.1400072511896724</v>
       </c>
       <c r="O11" s="5">
         <v>5</v>
       </c>
       <c r="P11" s="4">
-        <v>0.7272246043213575</v>
+        <v>0.7198362711781859</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1223130640483578</v>
+        <v>0.1178800641624548</v>
       </c>
       <c r="R11" s="5">
         <v>5</v>
@@ -11118,16 +11118,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4750027826095383</v>
+        <v>-0.4374005953068263</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2810663407000568</v>
+        <v>0.2756945996568123</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2810663407000568</v>
+        <v>0.2756945996568123</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -11177,16 +11177,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.6325267440874346</v>
+        <v>-0.5607554017042276</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1931517015342548</v>
+        <v>0.1828986526223681</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1931517015342548</v>
+        <v>0.1828986526223681</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -11236,16 +11236,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.7861187090851066</v>
+        <v>-0.6909211089932796</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1522517301849196</v>
+        <v>0.1498044469431729</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1771971647059319</v>
+        <v>0.1584757342419228</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -11295,16 +11295,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.6575148421803273</v>
+        <v>-0.6473805045825429</v>
       </c>
       <c r="O6" s="5">
         <v>7</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1188717762504856</v>
+        <v>0.1174240137365164</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1188717762504856</v>
+        <v>0.1174240137365164</v>
       </c>
       <c r="R6" s="5">
         <v>7</v>
@@ -11354,16 +11354,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.2122257811222101</v>
+        <v>-0.1978258162671409</v>
       </c>
       <c r="O7" s="5">
         <v>7</v>
       </c>
       <c r="P7" s="4">
-        <v>0.09427727532156682</v>
+        <v>0.09222013748512836</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.09427727532156682</v>
+        <v>0.09222013748512836</v>
       </c>
       <c r="R7" s="5">
         <v>7</v>
@@ -11466,16 +11466,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.09552232096497651</v>
+        <v>0.01093878521351144</v>
       </c>
       <c r="O9" s="5">
         <v>7</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2205383512660699</v>
+        <v>0.2053296218120002</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2205383512660699</v>
+        <v>0.2053296218120002</v>
       </c>
       <c r="R9" s="5">
         <v>7</v>
@@ -11525,16 +11525,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.3112645395255337</v>
+        <v>-0.2695476222834259</v>
       </c>
       <c r="O10" s="5">
         <v>6</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1437427069559774</v>
+        <v>0.1431602167597573</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1088940819301772</v>
+        <v>0.1012616904942358</v>
       </c>
       <c r="R10" s="5">
         <v>6</v>
@@ -11584,16 +11584,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.4683492495575289</v>
+        <v>-0.3825805044216395</v>
       </c>
       <c r="O11" s="5">
         <v>6</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2264393085651035</v>
+        <v>0.205032900952574</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.2264393085651035</v>
+        <v>0.205032900952574</v>
       </c>
       <c r="R11" s="5">
         <v>6</v>
@@ -11766,16 +11766,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1398973006528519</v>
+        <v>-0.08734043233562261</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08266448794091381</v>
+        <v>0.07515636389559534</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08266448794091381</v>
+        <v>0.07515636389559534</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -11825,16 +11825,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2522059183403534</v>
+        <v>-0.2061016630177619</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.07835679955285148</v>
+        <v>0.05524066983759569</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07835679955285148</v>
+        <v>0.05524066983759569</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -11884,16 +11884,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2518374191214597</v>
+        <v>-0.239629375464574</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.06061358265718327</v>
+        <v>0.05886957642048531</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06061358265718327</v>
+        <v>0.05886957642048531</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -11943,13 +11943,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.318557709648303</v>
+        <v>-0.3158664770126052</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
       </c>
       <c r="P6" s="4">
-        <v>0.05729843929865248</v>
+        <v>0.05768290110375217</v>
       </c>
       <c r="Q6" s="4">
         <v>0.06452809380910669</v>
@@ -12002,16 +12002,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.1235483230999914</v>
+        <v>-0.1192778955719405</v>
       </c>
       <c r="O7" s="5">
         <v>6</v>
       </c>
       <c r="P7" s="4">
-        <v>0.3144143893125494</v>
+        <v>0.3138043282371135</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1632546937368413</v>
+        <v>0.1632546937368412</v>
       </c>
       <c r="R7" s="5">
         <v>6</v>
@@ -12118,16 +12118,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.168933230582687</v>
+        <v>0.1359893474873388</v>
       </c>
       <c r="O9" s="5">
         <v>7</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2285490781520208</v>
+        <v>0.2238428091383997</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2285490781520208</v>
+        <v>0.2238428091383997</v>
       </c>
       <c r="R9" s="5">
         <v>7</v>
@@ -12177,20 +12177,22 @@
         <v>1</v>
       </c>
       <c r="N10" s="4">
-        <v>-2.447966590851657</v>
+        <v>0.1036392184396391</v>
       </c>
       <c r="O10" s="5">
         <v>7</v>
       </c>
       <c r="P10" s="4">
-        <v>4.391510601833015</v>
-      </c>
-      <c r="Q10" s="4"/>
+        <v>2.690258658849156</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.151652949372874</v>
+      </c>
       <c r="R10" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S10" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="25" customHeight="1">
@@ -12234,16 +12236,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.1067511353849113</v>
+        <v>-0.07500261389395746</v>
       </c>
       <c r="O11" s="5">
         <v>6</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1744959736570308</v>
+        <v>0.1646247148679928</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1744959736570308</v>
+        <v>0.1646247148679928</v>
       </c>
       <c r="R11" s="5">
         <v>6</v>
@@ -12416,16 +12418,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3832704168650837</v>
+        <v>-0.3742911993758753</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1767781227273209</v>
+        <v>0.1754953773717196</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1767781227273209</v>
+        <v>0.1754953773717196</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -12475,16 +12477,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4536368223541233</v>
+        <v>-0.3892761625975254</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1523575537801811</v>
+        <v>0.1431631738149528</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1523575537801811</v>
+        <v>0.1431631738149528</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -12534,16 +12536,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.53435024357168</v>
+        <v>-0.5766831363507663</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1565263569458953</v>
+        <v>0.1504788008345973</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1565263569458953</v>
+        <v>0.1504788008345973</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -12593,16 +12595,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.5291655039213116</v>
+        <v>-0.5965251064044423</v>
       </c>
       <c r="O6" s="5">
         <v>7</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1843387210585428</v>
+        <v>0.1747159207038099</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1843387210585428</v>
+        <v>0.1747159207038099</v>
       </c>
       <c r="R6" s="5">
         <v>7</v>
@@ -12652,16 +12654,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.3534844553236326</v>
+        <v>-0.258896496885427</v>
       </c>
       <c r="O7" s="5">
         <v>5</v>
       </c>
       <c r="P7" s="4">
-        <v>0.3465259882066415</v>
+        <v>0.3330134227154694</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.381854755662498</v>
+        <v>0.362937163974857</v>
       </c>
       <c r="R7" s="5">
         <v>5</v>
@@ -12768,16 +12770,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.008897932243728843</v>
+        <v>0.03328169209271437</v>
       </c>
       <c r="O9" s="5">
         <v>7</v>
       </c>
       <c r="P9" s="4">
-        <v>0.4604825214522936</v>
+        <v>0.4569991271881528</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.4604825214522936</v>
+        <v>0.4569991271881528</v>
       </c>
       <c r="R9" s="5">
         <v>7</v>
@@ -12827,16 +12829,16 @@
         <v>1</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.4572304554369891</v>
+        <v>-0.09359162477630889</v>
       </c>
       <c r="O10" s="5">
         <v>7</v>
       </c>
       <c r="P10" s="4">
-        <v>0.7222311566421958</v>
+        <v>0.5423869683587067</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.4213015080412809</v>
+        <v>0.1508768166004302</v>
       </c>
       <c r="R10" s="5">
         <v>6</v>
@@ -12886,16 +12888,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.5043624554036796</v>
+        <v>-0.4245979970273766</v>
       </c>
       <c r="O11" s="5">
         <v>6</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2447910492325415</v>
+        <v>0.2186294355142309</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.2447910492325415</v>
+        <v>0.2186294355142309</v>
       </c>
       <c r="R11" s="5">
         <v>6</v>
@@ -13068,16 +13070,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2677892445759166</v>
+        <v>-0.2823397642932832</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.07543451848264061</v>
+        <v>0.0733558728087311</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.07543451848264061</v>
+        <v>0.0733558728087311</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -13127,16 +13129,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3020672856000601</v>
+        <v>-0.3142310109033133</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.0722273300073409</v>
+        <v>0.07048965496401902</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.0722273300073409</v>
+        <v>0.07048965496401902</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -13186,16 +13188,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2562480500117609</v>
+        <v>-0.237416856802156</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.04359722768261848</v>
+        <v>0.04090705722410348</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.04359722768261848</v>
+        <v>0.04090705722410348</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -13245,13 +13247,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.2619450367431758</v>
+        <v>-0.2644682060872583</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
       </c>
       <c r="P6" s="4">
-        <v>0.03800047432412699</v>
+        <v>0.03764002156068662</v>
       </c>
       <c r="Q6" s="4">
         <v>0.03796747007557618</v>
@@ -13304,16 +13306,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.0726232160480625</v>
+        <v>-0.1210778590975679</v>
       </c>
       <c r="O7" s="5">
         <v>6</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2779310435458423</v>
+        <v>0.2724711492592178</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1075466550741516</v>
+        <v>0.09310100456483876</v>
       </c>
       <c r="R7" s="5">
         <v>6</v>
@@ -13420,16 +13422,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.2711986960551128</v>
+        <v>0.1790372349205427</v>
       </c>
       <c r="O9" s="5">
         <v>7</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2148944836333204</v>
+        <v>0.2017285606140961</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2148944836333204</v>
+        <v>0.2017285606140961</v>
       </c>
       <c r="R9" s="5">
         <v>7</v>
@@ -13479,13 +13481,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.02318638298250638</v>
+        <v>0.02165292755307746</v>
       </c>
       <c r="O10" s="5">
         <v>6</v>
       </c>
       <c r="P10" s="4">
-        <v>1.599726599235163</v>
+        <v>1.599507534173816</v>
       </c>
       <c r="Q10" s="4">
         <v>0.0698196430682098</v>
@@ -13538,16 +13540,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.0002128766021390523</v>
+        <v>-0.09676652436610311</v>
       </c>
       <c r="O11" s="5">
         <v>6</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2150747691064478</v>
+        <v>0.1939781949652873</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.2150747691064478</v>
+        <v>0.1939781949652873</v>
       </c>
       <c r="R11" s="5">
         <v>6</v>
